--- a/qmit-test/element-survey.xlsx
+++ b/qmit-test/element-survey.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="58">
+<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="61">
   <x:si>
     <x:t>a</x:t>
   </x:si>
@@ -45,6 +45,9 @@
     <x:t>div</x:t>
   </x:si>
   <x:si>
+    <x:t>class만으로 하나를 지목할 수 있었던 것 : 2개</x:t>
+  </x:si>
+  <x:si>
     <x:t>요소 설명</x:t>
   </x:si>
   <x:si>
@@ -54,6 +57,9 @@
     <x:t>비교 견적 의뢰 체크박스</x:t>
   </x:si>
   <x:si>
+    <x:t>갯수가 1이 아닐 경우 : btn의 갯수가 여러개이므로 "비교 견적 의뢰 체크박스"요소를 찾기 위해서는 위치나 상위 클래스를 같이 적어 해당 요소만 지정될 수 있어야 할 것 같습니다.</x:t>
+  </x:si>
+  <x:si>
     <x:t>메인</x:t>
   </x:si>
   <x:si>
@@ -130,6 +136,9 @@
   </x:si>
   <x:si>
     <x:t>이메일을 입력해주세요.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>data-cy로 지목 가능한 것 : 2개</x:t>
   </x:si>
   <x:si>
     <x:t>제목을 입력해주세요.</x:t>
@@ -274,7 +283,7 @@
       <x:alignment horizontal="general" vertical="center"/>
     </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="4">
+  <x:cellXfs count="7">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <x:alignment horizontal="general" vertical="center"/>
     </x:xf>
@@ -307,6 +316,15 @@
         </x:xf>
       </mc:Fallback>
     </mc:AlternateContent>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="center"/>
+    </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="표준" xfId="0" builtinId="0" iLevel="0"/>
@@ -1027,7 +1045,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetPr codeName="Sheet1"/>
-  <x:dimension ref="B2:I17"/>
+  <x:dimension ref="B2:I21"/>
   <x:sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="16.399999999999999"/>
   <x:cols>
     <x:col min="1" max="1" width="3.69921875" customWidth="1"/>
@@ -1042,152 +1060,152 @@
   <x:sheetData>
     <x:row r="2" spans="2:9">
       <x:c r="B2" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C2" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="D2" s="1" t="s">
         <x:v>2</x:v>
       </x:c>
       <x:c r="E2" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="F2" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="G2" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="H2" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="I2" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>36</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="2:9">
       <x:c r="B3" s="2" t="s">
-        <x:v>11</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="C3" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="D3" s="1" t="s">
         <x:v>7</x:v>
       </x:c>
       <x:c r="E3" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="F3" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G3" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="H3" s="1">
         <x:v>1</x:v>
       </x:c>
       <x:c r="I3" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>45</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="2:9">
       <x:c r="B4" s="2" t="s">
-        <x:v>11</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="C4" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="D4" s="1" t="s">
-        <x:v>9</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E4" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="F4" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G4" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="H4" s="1">
         <x:v>1</x:v>
       </x:c>
       <x:c r="I4" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>55</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="2:9">
       <x:c r="B5" s="2" t="s">
-        <x:v>11</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="C5" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="D5" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="E5" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="F5" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G5" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="H5" s="1">
         <x:v>1</x:v>
       </x:c>
       <x:c r="I5" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>60</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="2:9">
       <x:c r="B6" s="2" t="s">
-        <x:v>11</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="C6" s="3" t="s">
-        <x:v>33</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D6" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="E6" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="F6" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G6" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="H6" s="1">
         <x:v>1</x:v>
       </x:c>
       <x:c r="I6" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>48</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="2:9">
       <x:c r="B7" s="2" t="s">
-        <x:v>11</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="C7" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="D7" s="1" t="s">
         <x:v>0</x:v>
       </x:c>
       <x:c r="E7" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="F7" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G7" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="H7" s="1">
         <x:v>1</x:v>
@@ -1201,25 +1219,25 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="C8" s="3" t="s">
-        <x:v>22</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="D8" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="E8" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="F8" s="3" t="s">
-        <x:v>24</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="G8" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="H8" s="1">
         <x:v>1</x:v>
       </x:c>
       <x:c r="I8" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>58</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="2:9">
@@ -1230,13 +1248,13 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="D9" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="E9" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="F9" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G9" s="1" t="s">
         <x:v>3</x:v>
@@ -1245,7 +1263,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I9" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>46</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="2:9">
@@ -1253,25 +1271,25 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="C10" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="D10" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="E10" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="F10" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="G10" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="H10" s="1">
         <x:v>1</x:v>
       </x:c>
       <x:c r="I10" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>54</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="2:9">
@@ -1279,19 +1297,19 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="C11" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="D11" s="1" t="s">
         <x:v>7</x:v>
       </x:c>
       <x:c r="E11" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="F11" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G11" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="H11" s="1">
         <x:v>32</x:v>
@@ -1305,19 +1323,19 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="C12" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="D12" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="E12" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="F12" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G12" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="H12" s="1">
         <x:v>1</x:v>
@@ -1328,135 +1346,167 @@
     </x:row>
     <x:row r="13" spans="2:9">
       <x:c r="B13" s="2" t="s">
-        <x:v>13</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="C13" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="D13" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="E13" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="F13" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G13" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="H13" s="1">
         <x:v>1</x:v>
       </x:c>
       <x:c r="I13" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="2:9">
       <x:c r="B14" s="2" t="s">
-        <x:v>13</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="C14" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="D14" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="E14" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="F14" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G14" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="H14" s="1">
         <x:v>1</x:v>
       </x:c>
       <x:c r="I14" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>27</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="2:9">
       <x:c r="B15" s="2" t="s">
-        <x:v>13</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="C15" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="D15" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="E15" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="F15" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="G15" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="H15" s="1">
         <x:v>1</x:v>
       </x:c>
       <x:c r="I15" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>59</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="2:9">
       <x:c r="B16" s="2" t="s">
-        <x:v>13</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="C16" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="D16" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="E16" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="F16" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G16" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="H16" s="1">
         <x:v>1</x:v>
       </x:c>
       <x:c r="I16" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>52</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="2:9">
       <x:c r="B17" s="2" t="s">
-        <x:v>13</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="C17" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="D17" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="E17" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F17" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="G17" s="1" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="H17" s="1">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I17" s="1" t="s">
+        <x:v>43</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" spans="2:5">
+      <x:c r="B19" s="4" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="C19" s="4"/>
+      <x:c r="D19" s="4"/>
+      <x:c r="E19" s="4"/>
+    </x:row>
+    <x:row r="20" spans="2:5">
+      <x:c r="B20" s="4" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="C20" s="4"/>
+      <x:c r="D20" s="4"/>
+      <x:c r="E20" s="4"/>
+    </x:row>
+    <x:row r="21" spans="2:9">
+      <x:c r="B21" s="5" t="s">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="F17" s="1" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="G17" s="1" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="H17" s="1">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="I17" s="1" t="s">
-        <x:v>40</x:v>
-      </x:c>
+      <x:c r="C21" s="5"/>
+      <x:c r="D21" s="5"/>
+      <x:c r="E21" s="5"/>
+      <x:c r="F21" s="5"/>
+      <x:c r="G21" s="6"/>
+      <x:c r="H21" s="6"/>
+      <x:c r="I21" s="6"/>
     </x:row>
   </x:sheetData>
+  <x:mergeCells count="2">
+    <x:mergeCell ref="B19:E19"/>
+    <x:mergeCell ref="B20:E20"/>
+  </x:mergeCells>
   <x:pageMargins left="0.74805557727813721" right="0.74805557727813721" top="0.98430556058883667" bottom="0.98430556058883667" header="0.51180553436279297" footer="0.51180553436279297"/>
   <x:pageSetup paperSize="9" scale="100" firstPageNumber="1" fitToWidth="0" fitToHeight="0" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" useFirstPageNumber="0" horizontalDpi="600" verticalDpi="600" copies="1"/>
 </x:worksheet>
